--- a/out/sessions/blur_scaler-20251114_184757/blur_scaler.xlsx
+++ b/out/sessions/blur_scaler-20251114_184757/blur_scaler.xlsx
@@ -2839,6 +2839,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L10" s="245" t="inlineStr">
+        <is>
+          <t>i_enable</t>
+        </is>
+      </c>
+      <c r="M10" s="245" t="inlineStr">
+        <is>
+          <t>i_blur_mode_cap &amp;&amp; i_den</t>
+        </is>
+      </c>
+      <c r="N10" s="245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="E11" s="245" t="inlineStr">
@@ -2947,16 +2962,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I14" s="245" t="inlineStr">
-        <is>
-          <t>VBLANK</t>
-        </is>
-      </c>
-      <c r="J14" s="245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" s="245" t="n"/>
+      <c r="J14" s="245" t="n"/>
     </row>
     <row r="15">
       <c r="E15" s="245" t="inlineStr">
@@ -2969,16 +2976,8 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I15" s="245" t="inlineStr">
-        <is>
-          <t>HBLANK</t>
-        </is>
-      </c>
-      <c r="J15" s="245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" s="245" t="n"/>
+      <c r="J15" s="245" t="n"/>
     </row>
     <row r="16">
       <c r="E16" s="245" t="inlineStr">
